--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89220</v>
+        <v>89226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89226</v>
+        <v>89230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89230</v>
+        <v>89232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89232</v>
+        <v>89245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89245</v>
+        <v>89247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89247</v>
+        <v>89250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89250</v>
+        <v>89260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89260</v>
+        <v>89261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89261</v>
+        <v>89264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89264</v>
+        <v>89269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89269</v>
+        <v>89280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89280</v>
+        <v>89281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89281</v>
+        <v>89284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31693-2026 artfynd.xlsx
+++ b/artfynd/A 31693-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124471</v>
       </c>
       <c r="B2" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124469</v>
       </c>
       <c r="B3" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124436</v>
       </c>
       <c r="B4" t="n">
-        <v>89284</v>
+        <v>89288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137124440</v>
       </c>
       <c r="B5" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137124442</v>
       </c>
       <c r="B6" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137124437</v>
       </c>
       <c r="B7" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137124438</v>
       </c>
       <c r="B8" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137124441</v>
       </c>
       <c r="B9" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137124467</v>
       </c>
       <c r="B10" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137124468</v>
       </c>
       <c r="B11" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137124470</v>
       </c>
       <c r="B12" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
